--- a/docs/12_画面定義書/12_00_ひな形_画面定義書.xlsx
+++ b/docs/12_画面定義書/12_00_ひな形_画面定義書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nishikawaaoi/Desktop/java/設計書/02_画面定義書/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nishikawaaoi/workspace_study/docs/12_画面定義書/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2D7C11-4361-E54E-9C67-FA0B3FE73FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6C4633-EE35-914B-B842-7A1A1F716739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16540" xr2:uid="{55AC04BD-A38B-4D4E-ACF8-55E49DC581E1}"/>
+    <workbookView xWindow="0" yWindow="520" windowWidth="28800" windowHeight="16440" activeTab="2" xr2:uid="{55AC04BD-A38B-4D4E-ACF8-55E49DC581E1}"/>
   </bookViews>
   <sheets>
     <sheet name="変更履歴" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="サンプル_画面" sheetId="5" r:id="rId3"/>
     <sheet name="サンプル_項目" sheetId="6" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="51">
   <si>
     <t>項番</t>
     <rPh sb="0" eb="2">
@@ -194,13 +194,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>全体のカラー</t>
-    <rPh sb="0" eb="2">
-      <t>ゼンタイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>フォント</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -215,15 +208,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ヒラギノ角ゴ StdN</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ラベル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ヒラギノ角ゴ Pro</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -245,20 +230,6 @@
     <t>備考</t>
     <rPh sb="0" eb="2">
       <t>ビコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ダークグレー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>白、黒、ライトグレー、グレー、ダークグレー</t>
-    <rPh sb="0" eb="1">
-      <t>シロ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>クロ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -277,10 +248,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>GAME</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>トランプゲーム</t>
     <rPh sb="0" eb="1">
       <t>モドル</t>
@@ -292,10 +259,68 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>白</t>
-    <rPh sb="0" eb="1">
-      <t xml:space="preserve">シロ </t>
+    <t>場所</t>
+    <rPh sb="0" eb="2">
+      <t>バショ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>header</t>
+  </si>
+  <si>
+    <t>項番</t>
+    <rPh sb="0" eb="2">
+      <t>コウバn</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画像</t>
+    <rPh sb="0" eb="2">
+      <t>ガゾウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム選択</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Zen Kaku Gothic New</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>white</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>≡</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Zen Kaku Gothic New</t>
+  </si>
+  <si>
+    <t>main</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>○</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -303,7 +328,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -347,6 +372,24 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF00B0F0"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -508,7 +551,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -533,14 +576,29 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -552,94 +610,64 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1567,691 +1595,1159 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B2:BQ21"/>
+  <dimension ref="B2:BU28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="3.7109375" defaultRowHeight="20"/>
   <sheetData>
-    <row r="2" spans="2:69">
+    <row r="2" spans="2:73">
       <c r="B2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:69">
+    <row r="3" spans="2:73">
       <c r="C3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:69">
-      <c r="AP4" s="11" t="s">
+    <row r="4" spans="2:73">
+      <c r="AP4" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ4" s="17"/>
+      <c r="AR4" s="17"/>
+      <c r="AS4" s="17"/>
+      <c r="AT4" s="18"/>
+      <c r="AU4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="AV4" s="12"/>
+      <c r="AW4" s="12"/>
+      <c r="AX4" s="12"/>
+      <c r="AY4" s="12"/>
+      <c r="AZ4" s="12"/>
+      <c r="BA4" s="12"/>
+      <c r="BB4" s="13"/>
+      <c r="BC4" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="BD4" s="17"/>
+      <c r="BE4" s="17"/>
+      <c r="BF4" s="17"/>
+      <c r="BG4" s="17"/>
+      <c r="BH4" s="18"/>
+      <c r="BI4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="BJ4" s="12"/>
+      <c r="BK4" s="12"/>
+      <c r="BL4" s="12"/>
+      <c r="BM4" s="12"/>
+      <c r="BN4" s="12"/>
+      <c r="BO4" s="12"/>
+      <c r="BP4" s="12"/>
+      <c r="BQ4" s="12"/>
+      <c r="BR4" s="12"/>
+      <c r="BS4" s="12"/>
+      <c r="BT4" s="12"/>
+      <c r="BU4" s="13"/>
+    </row>
+    <row r="5" spans="2:73">
+      <c r="AP5" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ5" s="20"/>
+      <c r="AR5" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="AS5" s="21"/>
+      <c r="AT5" s="21"/>
+      <c r="AU5" s="21"/>
+      <c r="AV5" s="21"/>
+      <c r="AW5" s="20"/>
+      <c r="AX5" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="AY5" s="20"/>
+      <c r="AZ5" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="AQ4" s="12"/>
-      <c r="AR4" s="12"/>
-      <c r="AS4" s="12"/>
-      <c r="AT4" s="12"/>
-      <c r="AU4" s="13"/>
-      <c r="AV4" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="AW4" s="37"/>
-      <c r="AX4" s="37"/>
-      <c r="AY4" s="37"/>
-      <c r="AZ4" s="37"/>
-      <c r="BA4" s="37"/>
-      <c r="BB4" s="37"/>
-      <c r="BC4" s="37"/>
-      <c r="BD4" s="37"/>
-      <c r="BE4" s="37"/>
-      <c r="BF4" s="37"/>
-      <c r="BG4" s="37"/>
-      <c r="BH4" s="37"/>
-      <c r="BI4" s="37"/>
-      <c r="BJ4" s="37"/>
-      <c r="BK4" s="37"/>
-      <c r="BL4" s="37"/>
-      <c r="BM4" s="37"/>
-      <c r="BN4" s="37"/>
-      <c r="BO4" s="37"/>
-      <c r="BP4" s="37"/>
-      <c r="BQ4" s="38"/>
-    </row>
-    <row r="5" spans="2:69">
-      <c r="AP5" s="11" t="s">
+      <c r="BA5" s="21"/>
+      <c r="BB5" s="21"/>
+      <c r="BC5" s="21"/>
+      <c r="BD5" s="20"/>
+      <c r="BE5" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="BF5" s="21"/>
+      <c r="BG5" s="20"/>
+      <c r="BH5" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI5" s="21"/>
+      <c r="BJ5" s="20"/>
+      <c r="BK5" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="BL5" s="20"/>
+      <c r="BM5" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="BN5" s="21"/>
+      <c r="BO5" s="21"/>
+      <c r="BP5" s="20"/>
+      <c r="BQ5" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="AQ5" s="12"/>
-      <c r="AR5" s="12"/>
-      <c r="AS5" s="12"/>
-      <c r="AT5" s="12"/>
-      <c r="AU5" s="13"/>
-      <c r="AV5" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="AW5" s="37"/>
-      <c r="AX5" s="37"/>
-      <c r="AY5" s="37"/>
-      <c r="AZ5" s="37"/>
-      <c r="BA5" s="37"/>
-      <c r="BB5" s="37"/>
-      <c r="BC5" s="37"/>
-      <c r="BD5" s="37"/>
-      <c r="BE5" s="37"/>
-      <c r="BF5" s="37"/>
-      <c r="BG5" s="37"/>
-      <c r="BH5" s="37"/>
-      <c r="BI5" s="37"/>
-      <c r="BJ5" s="37"/>
-      <c r="BK5" s="37"/>
-      <c r="BL5" s="37"/>
-      <c r="BM5" s="37"/>
-      <c r="BN5" s="37"/>
-      <c r="BO5" s="37"/>
-      <c r="BP5" s="37"/>
-      <c r="BQ5" s="38"/>
-    </row>
-    <row r="6" spans="2:69" ht="20" customHeight="1"/>
-    <row r="7" spans="2:69" ht="20" customHeight="1">
-      <c r="AP7" s="14"/>
-      <c r="AQ7" s="15"/>
-      <c r="AR7" s="15"/>
-      <c r="AS7" s="15"/>
-      <c r="AT7" s="15"/>
-      <c r="AU7" s="16"/>
-      <c r="AV7" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="AW7" s="15"/>
-      <c r="AX7" s="15"/>
+      <c r="BR5" s="21"/>
+      <c r="BS5" s="21"/>
+      <c r="BT5" s="21"/>
+      <c r="BU5" s="20"/>
+    </row>
+    <row r="6" spans="2:73" ht="20" customHeight="1">
+      <c r="AP6" s="22"/>
+      <c r="AQ6" s="23"/>
+      <c r="AR6" s="22"/>
+      <c r="AS6" s="24"/>
+      <c r="AT6" s="24"/>
+      <c r="AU6" s="24"/>
+      <c r="AV6" s="24"/>
+      <c r="AW6" s="23"/>
+      <c r="AX6" s="22"/>
+      <c r="AY6" s="23"/>
+      <c r="AZ6" s="22"/>
+      <c r="BA6" s="24"/>
+      <c r="BB6" s="24"/>
+      <c r="BC6" s="24"/>
+      <c r="BD6" s="23"/>
+      <c r="BE6" s="22"/>
+      <c r="BF6" s="24"/>
+      <c r="BG6" s="23"/>
+      <c r="BH6" s="22"/>
+      <c r="BI6" s="24"/>
+      <c r="BJ6" s="23"/>
+      <c r="BK6" s="22"/>
+      <c r="BL6" s="23"/>
+      <c r="BM6" s="22"/>
+      <c r="BN6" s="24"/>
+      <c r="BO6" s="24"/>
+      <c r="BP6" s="23"/>
+      <c r="BQ6" s="22"/>
+      <c r="BR6" s="24"/>
+      <c r="BS6" s="24"/>
+      <c r="BT6" s="24"/>
+      <c r="BU6" s="23"/>
+    </row>
+    <row r="7" spans="2:73" ht="20" customHeight="1">
+      <c r="AP7" s="25">
+        <f>IF(AR7="","",ROW()-6)</f>
+        <v>1</v>
+      </c>
+      <c r="AQ7" s="26"/>
+      <c r="AR7" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS7" s="28"/>
+      <c r="AT7" s="28"/>
+      <c r="AU7" s="28"/>
+      <c r="AV7" s="28"/>
+      <c r="AW7" s="29"/>
+      <c r="AX7" s="14" t="s">
+        <v>43</v>
+      </c>
       <c r="AY7" s="15"/>
-      <c r="AZ7" s="16"/>
-      <c r="BA7" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="BB7" s="21"/>
-      <c r="BC7" s="22"/>
-      <c r="BD7" s="20" t="s">
+      <c r="AZ7" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="12"/>
+      <c r="BC7" s="12"/>
+      <c r="BD7" s="13"/>
+      <c r="BE7" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF7" s="12"/>
+      <c r="BG7" s="13"/>
+      <c r="BH7" s="11">
+        <v>18</v>
+      </c>
+      <c r="BI7" s="12"/>
+      <c r="BJ7" s="13"/>
+      <c r="BK7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="BL7" s="13"/>
+      <c r="BM7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="BE7" s="21"/>
-      <c r="BF7" s="22"/>
-      <c r="BG7" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="BH7" s="26"/>
-      <c r="BI7" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="BJ7" s="15"/>
-      <c r="BK7" s="15"/>
-      <c r="BL7" s="16"/>
-      <c r="BM7" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="BN7" s="15"/>
-      <c r="BO7" s="15"/>
-      <c r="BP7" s="15"/>
-      <c r="BQ7" s="16"/>
-    </row>
-    <row r="8" spans="2:69">
-      <c r="AP8" s="17"/>
-      <c r="AQ8" s="18"/>
-      <c r="AR8" s="18"/>
-      <c r="AS8" s="18"/>
-      <c r="AT8" s="18"/>
-      <c r="AU8" s="19"/>
-      <c r="AV8" s="17"/>
-      <c r="AW8" s="18"/>
-      <c r="AX8" s="18"/>
-      <c r="AY8" s="18"/>
-      <c r="AZ8" s="19"/>
-      <c r="BA8" s="23"/>
-      <c r="BB8" s="24"/>
-      <c r="BC8" s="25"/>
-      <c r="BD8" s="23"/>
-      <c r="BE8" s="24"/>
-      <c r="BF8" s="25"/>
-      <c r="BG8" s="26"/>
-      <c r="BH8" s="26"/>
-      <c r="BI8" s="17"/>
-      <c r="BJ8" s="18"/>
-      <c r="BK8" s="18"/>
-      <c r="BL8" s="19"/>
-      <c r="BM8" s="17"/>
-      <c r="BN8" s="18"/>
-      <c r="BO8" s="18"/>
-      <c r="BP8" s="18"/>
-      <c r="BQ8" s="19"/>
-    </row>
-    <row r="9" spans="2:69">
-      <c r="AP9" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="AQ9" s="28"/>
-      <c r="AR9" s="28"/>
-      <c r="AS9" s="28"/>
-      <c r="AT9" s="28"/>
-      <c r="AU9" s="29"/>
-      <c r="AV9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AW9" s="4"/>
-      <c r="AX9" s="4"/>
-      <c r="AY9" s="4"/>
-      <c r="AZ9" s="4"/>
-      <c r="BA9" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="BB9" s="37"/>
-      <c r="BC9" s="38"/>
-      <c r="BD9" s="30">
+      <c r="BN7" s="12"/>
+      <c r="BO7" s="12"/>
+      <c r="BP7" s="13"/>
+      <c r="BQ7" s="11"/>
+      <c r="BR7" s="12"/>
+      <c r="BS7" s="12"/>
+      <c r="BT7" s="12"/>
+      <c r="BU7" s="13"/>
+    </row>
+    <row r="8" spans="2:73">
+      <c r="AP8" s="25">
+        <f t="shared" ref="AP8:AP11" si="0">IF(AR8="","",ROW()-6)</f>
+        <v>2</v>
+      </c>
+      <c r="AQ8" s="26"/>
+      <c r="AR8" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="13"/>
+      <c r="AX8" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AY8" s="15"/>
+      <c r="AZ8" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="13"/>
+      <c r="BE8" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="13"/>
+      <c r="BH8" s="11">
         <v>18</v>
       </c>
-      <c r="BE9" s="31"/>
-      <c r="BF9" s="32"/>
-      <c r="BG9" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="BH9" s="32"/>
-      <c r="BI9" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="BJ9" s="37"/>
-      <c r="BK9" s="37"/>
-      <c r="BL9" s="38"/>
-      <c r="BM9" s="36"/>
-      <c r="BN9" s="37"/>
-      <c r="BO9" s="37"/>
-      <c r="BP9" s="37"/>
-      <c r="BQ9" s="38"/>
-    </row>
-    <row r="10" spans="2:69">
-      <c r="AP10" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ10" s="12"/>
-      <c r="AR10" s="12"/>
+      <c r="BI8" s="12"/>
+      <c r="BJ8" s="13"/>
+      <c r="BK8" s="11"/>
+      <c r="BL8" s="13"/>
+      <c r="BM8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="BN8" s="9"/>
+      <c r="BO8" s="9"/>
+      <c r="BP8" s="10"/>
+      <c r="BQ8" s="8"/>
+      <c r="BR8" s="9"/>
+      <c r="BS8" s="9"/>
+      <c r="BT8" s="9"/>
+      <c r="BU8" s="10"/>
+    </row>
+    <row r="9" spans="2:73">
+      <c r="AP9" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AQ9" s="26"/>
+      <c r="AR9" s="11"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="13"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="15"/>
+      <c r="AZ9" s="11"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="13"/>
+      <c r="BE9" s="11"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="13"/>
+      <c r="BH9" s="11"/>
+      <c r="BI9" s="12"/>
+      <c r="BJ9" s="13"/>
+      <c r="BK9" s="11"/>
+      <c r="BL9" s="13"/>
+      <c r="BM9" s="8"/>
+      <c r="BN9" s="9"/>
+      <c r="BO9" s="9"/>
+      <c r="BP9" s="10"/>
+      <c r="BQ9" s="11"/>
+      <c r="BR9" s="12"/>
+      <c r="BS9" s="12"/>
+      <c r="BT9" s="12"/>
+      <c r="BU9" s="13"/>
+    </row>
+    <row r="10" spans="2:73">
+      <c r="AP10" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AQ10" s="26"/>
+      <c r="AR10" s="11"/>
       <c r="AS10" s="12"/>
       <c r="AT10" s="12"/>
-      <c r="AU10" s="13"/>
-      <c r="AV10" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AW10" s="9"/>
-      <c r="AX10" s="9"/>
-      <c r="AY10" s="9"/>
-      <c r="AZ10" s="10"/>
-      <c r="BA10" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="BB10" s="37"/>
-      <c r="BC10" s="38"/>
-      <c r="BD10" s="30">
-        <v>28</v>
-      </c>
-      <c r="BE10" s="31"/>
-      <c r="BF10" s="32"/>
-      <c r="BG10" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="BH10" s="32"/>
-      <c r="BI10" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="BJ10" s="40"/>
-      <c r="BK10" s="40"/>
-      <c r="BL10" s="41"/>
-      <c r="BM10" s="39"/>
-      <c r="BN10" s="40"/>
-      <c r="BO10" s="40"/>
-      <c r="BP10" s="40"/>
-      <c r="BQ10" s="41"/>
-    </row>
-    <row r="11" spans="2:69">
-      <c r="AP11" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="AQ11" s="12"/>
-      <c r="AR11" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="13"/>
+      <c r="AX10" s="14"/>
+      <c r="AY10" s="15"/>
+      <c r="AZ10" s="11"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="13"/>
+      <c r="BE10" s="11"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="13"/>
+      <c r="BH10" s="11"/>
+      <c r="BI10" s="12"/>
+      <c r="BJ10" s="13"/>
+      <c r="BK10" s="11"/>
+      <c r="BL10" s="13"/>
+      <c r="BM10" s="11"/>
+      <c r="BN10" s="12"/>
+      <c r="BO10" s="12"/>
+      <c r="BP10" s="13"/>
+      <c r="BQ10" s="11"/>
+      <c r="BR10" s="12"/>
+      <c r="BS10" s="12"/>
+      <c r="BT10" s="12"/>
+      <c r="BU10" s="13"/>
+    </row>
+    <row r="11" spans="2:73">
+      <c r="AP11" s="25" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AQ11" s="26"/>
+      <c r="AR11" s="11"/>
       <c r="AS11" s="12"/>
       <c r="AT11" s="12"/>
-      <c r="AU11" s="13"/>
-      <c r="AV11" s="8" t="s">
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="13"/>
+      <c r="AX11" s="14"/>
+      <c r="AY11" s="15"/>
+      <c r="AZ11" s="11"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="13"/>
+      <c r="BE11" s="11"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="13"/>
+      <c r="BH11" s="11"/>
+      <c r="BI11" s="12"/>
+      <c r="BJ11" s="13"/>
+      <c r="BK11" s="11"/>
+      <c r="BL11" s="13"/>
+      <c r="BM11" s="11"/>
+      <c r="BN11" s="12"/>
+      <c r="BO11" s="12"/>
+      <c r="BP11" s="13"/>
+      <c r="BQ11" s="11"/>
+      <c r="BR11" s="12"/>
+      <c r="BS11" s="12"/>
+      <c r="BT11" s="12"/>
+      <c r="BU11" s="13"/>
+    </row>
+    <row r="14" spans="2:73">
+      <c r="AP14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ14" s="17"/>
+      <c r="AR14" s="17"/>
+      <c r="AS14" s="17"/>
+      <c r="AT14" s="18"/>
+      <c r="AU14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="13"/>
+      <c r="BC14" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="BD14" s="17"/>
+      <c r="BE14" s="17"/>
+      <c r="BF14" s="17"/>
+      <c r="BG14" s="17"/>
+      <c r="BH14" s="18"/>
+      <c r="BI14" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="BJ14" s="12"/>
+      <c r="BK14" s="12"/>
+      <c r="BL14" s="12"/>
+      <c r="BM14" s="12"/>
+      <c r="BN14" s="12"/>
+      <c r="BO14" s="12"/>
+      <c r="BP14" s="12"/>
+      <c r="BQ14" s="12"/>
+      <c r="BR14" s="12"/>
+      <c r="BS14" s="12"/>
+      <c r="BT14" s="12"/>
+      <c r="BU14" s="13"/>
+    </row>
+    <row r="15" spans="2:73">
+      <c r="AP15" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ15" s="20"/>
+      <c r="AR15" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="AS15" s="21"/>
+      <c r="AT15" s="21"/>
+      <c r="AU15" s="21"/>
+      <c r="AV15" s="21"/>
+      <c r="AW15" s="20"/>
+      <c r="AX15" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="AY15" s="20"/>
+      <c r="AZ15" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="BA15" s="21"/>
+      <c r="BB15" s="21"/>
+      <c r="BC15" s="21"/>
+      <c r="BD15" s="20"/>
+      <c r="BE15" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="BF15" s="21"/>
+      <c r="BG15" s="20"/>
+      <c r="BH15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI15" s="21"/>
+      <c r="BJ15" s="20"/>
+      <c r="BK15" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="BL15" s="20"/>
+      <c r="BM15" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="AW11" s="9"/>
-      <c r="AX11" s="9"/>
-      <c r="AY11" s="9"/>
-      <c r="AZ11" s="10"/>
-      <c r="BA11" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="BB11" s="37"/>
-      <c r="BC11" s="38"/>
-      <c r="BD11" s="30">
-        <v>28</v>
-      </c>
-      <c r="BE11" s="31"/>
-      <c r="BF11" s="32"/>
-      <c r="BG11" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="BH11" s="32"/>
-      <c r="BI11" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="BJ11" s="40"/>
-      <c r="BK11" s="40"/>
-      <c r="BL11" s="41"/>
-      <c r="BM11" s="36"/>
-      <c r="BN11" s="37"/>
-      <c r="BO11" s="37"/>
-      <c r="BP11" s="37"/>
-      <c r="BQ11" s="38"/>
-    </row>
-    <row r="12" spans="2:69">
-      <c r="AP12" s="11"/>
-      <c r="AQ12" s="12"/>
-      <c r="AR12" s="12"/>
-      <c r="AS12" s="12"/>
-      <c r="AT12" s="12"/>
-      <c r="AU12" s="13"/>
-      <c r="AV12" s="8"/>
-      <c r="AW12" s="9"/>
-      <c r="AX12" s="9"/>
-      <c r="AY12" s="9"/>
-      <c r="AZ12" s="10"/>
-      <c r="BA12" s="36"/>
-      <c r="BB12" s="37"/>
-      <c r="BC12" s="38"/>
-      <c r="BD12" s="30"/>
-      <c r="BE12" s="31"/>
-      <c r="BF12" s="32"/>
-      <c r="BG12" s="30"/>
-      <c r="BH12" s="32"/>
-      <c r="BI12" s="36"/>
-      <c r="BJ12" s="37"/>
-      <c r="BK12" s="37"/>
-      <c r="BL12" s="38"/>
-      <c r="BM12" s="36"/>
-      <c r="BN12" s="37"/>
-      <c r="BO12" s="37"/>
-      <c r="BP12" s="37"/>
-      <c r="BQ12" s="38"/>
-    </row>
-    <row r="13" spans="2:69">
-      <c r="AP13" s="11"/>
-      <c r="AQ13" s="12"/>
-      <c r="AR13" s="12"/>
-      <c r="AS13" s="12"/>
-      <c r="AT13" s="12"/>
-      <c r="AU13" s="13"/>
-      <c r="AV13" s="8"/>
-      <c r="AW13" s="9"/>
-      <c r="AX13" s="9"/>
-      <c r="AY13" s="9"/>
-      <c r="AZ13" s="10"/>
-      <c r="BA13" s="36"/>
-      <c r="BB13" s="37"/>
-      <c r="BC13" s="38"/>
-      <c r="BD13" s="30"/>
-      <c r="BE13" s="31"/>
-      <c r="BF13" s="32"/>
-      <c r="BG13" s="30"/>
-      <c r="BH13" s="32"/>
-      <c r="BI13" s="36"/>
-      <c r="BJ13" s="37"/>
-      <c r="BK13" s="37"/>
-      <c r="BL13" s="38"/>
-      <c r="BM13" s="36"/>
-      <c r="BN13" s="37"/>
-      <c r="BO13" s="37"/>
-      <c r="BP13" s="37"/>
-      <c r="BQ13" s="38"/>
-    </row>
-    <row r="14" spans="2:69">
-      <c r="AP14" s="11"/>
-      <c r="AQ14" s="12"/>
-      <c r="AR14" s="12"/>
-      <c r="AS14" s="12"/>
-      <c r="AT14" s="12"/>
-      <c r="AU14" s="13"/>
-      <c r="AV14" s="8"/>
-      <c r="AW14" s="9"/>
-      <c r="AX14" s="9"/>
-      <c r="AY14" s="9"/>
-      <c r="AZ14" s="10"/>
-      <c r="BA14" s="36"/>
-      <c r="BB14" s="37"/>
-      <c r="BC14" s="38"/>
-      <c r="BD14" s="30"/>
-      <c r="BE14" s="31"/>
-      <c r="BF14" s="32"/>
-      <c r="BG14" s="30"/>
-      <c r="BH14" s="32"/>
-      <c r="BI14" s="36"/>
-      <c r="BJ14" s="37"/>
-      <c r="BK14" s="37"/>
-      <c r="BL14" s="38"/>
-      <c r="BM14" s="36"/>
-      <c r="BN14" s="37"/>
-      <c r="BO14" s="37"/>
-      <c r="BP14" s="37"/>
-      <c r="BQ14" s="38"/>
-    </row>
-    <row r="15" spans="2:69">
-      <c r="AP15" s="11"/>
-      <c r="AQ15" s="12"/>
-      <c r="AR15" s="12"/>
-      <c r="AS15" s="12"/>
-      <c r="AT15" s="12"/>
-      <c r="AU15" s="13"/>
-      <c r="AV15" s="8"/>
-      <c r="AW15" s="9"/>
-      <c r="AX15" s="9"/>
-      <c r="AY15" s="9"/>
-      <c r="AZ15" s="10"/>
-      <c r="BA15" s="36"/>
-      <c r="BB15" s="37"/>
-      <c r="BC15" s="38"/>
-      <c r="BD15" s="33"/>
-      <c r="BE15" s="34"/>
-      <c r="BF15" s="35"/>
-      <c r="BG15" s="30"/>
-      <c r="BH15" s="32"/>
-      <c r="BI15" s="36"/>
-      <c r="BJ15" s="37"/>
-      <c r="BK15" s="37"/>
-      <c r="BL15" s="38"/>
-      <c r="BM15" s="36"/>
-      <c r="BN15" s="37"/>
-      <c r="BO15" s="37"/>
-      <c r="BP15" s="37"/>
-      <c r="BQ15" s="38"/>
-    </row>
-    <row r="16" spans="2:69">
-      <c r="AP16" s="11"/>
-      <c r="AQ16" s="12"/>
-      <c r="AR16" s="12"/>
-      <c r="AS16" s="12"/>
-      <c r="AT16" s="12"/>
-      <c r="AU16" s="13"/>
-      <c r="AV16" s="8"/>
-      <c r="AW16" s="9"/>
-      <c r="AX16" s="9"/>
-      <c r="AY16" s="9"/>
-      <c r="AZ16" s="10"/>
-      <c r="BA16" s="36"/>
-      <c r="BB16" s="37"/>
-      <c r="BC16" s="38"/>
-      <c r="BD16" s="33"/>
-      <c r="BE16" s="34"/>
-      <c r="BF16" s="35"/>
-      <c r="BG16" s="30"/>
-      <c r="BH16" s="32"/>
-      <c r="BI16" s="36"/>
-      <c r="BJ16" s="37"/>
-      <c r="BK16" s="37"/>
-      <c r="BL16" s="38"/>
-      <c r="BM16" s="36"/>
-      <c r="BN16" s="37"/>
-      <c r="BO16" s="37"/>
-      <c r="BP16" s="37"/>
-      <c r="BQ16" s="38"/>
-    </row>
-    <row r="17" spans="42:69">
-      <c r="AP17" s="11"/>
-      <c r="AQ17" s="12"/>
-      <c r="AR17" s="12"/>
+      <c r="BN15" s="21"/>
+      <c r="BO15" s="21"/>
+      <c r="BP15" s="20"/>
+      <c r="BQ15" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="BR15" s="21"/>
+      <c r="BS15" s="21"/>
+      <c r="BT15" s="21"/>
+      <c r="BU15" s="20"/>
+    </row>
+    <row r="16" spans="2:73">
+      <c r="AP16" s="22"/>
+      <c r="AQ16" s="23"/>
+      <c r="AR16" s="22"/>
+      <c r="AS16" s="24"/>
+      <c r="AT16" s="24"/>
+      <c r="AU16" s="24"/>
+      <c r="AV16" s="24"/>
+      <c r="AW16" s="23"/>
+      <c r="AX16" s="22"/>
+      <c r="AY16" s="23"/>
+      <c r="AZ16" s="22"/>
+      <c r="BA16" s="24"/>
+      <c r="BB16" s="24"/>
+      <c r="BC16" s="24"/>
+      <c r="BD16" s="23"/>
+      <c r="BE16" s="22"/>
+      <c r="BF16" s="24"/>
+      <c r="BG16" s="23"/>
+      <c r="BH16" s="22"/>
+      <c r="BI16" s="24"/>
+      <c r="BJ16" s="23"/>
+      <c r="BK16" s="22"/>
+      <c r="BL16" s="23"/>
+      <c r="BM16" s="22"/>
+      <c r="BN16" s="24"/>
+      <c r="BO16" s="24"/>
+      <c r="BP16" s="23"/>
+      <c r="BQ16" s="22"/>
+      <c r="BR16" s="24"/>
+      <c r="BS16" s="24"/>
+      <c r="BT16" s="24"/>
+      <c r="BU16" s="23"/>
+    </row>
+    <row r="17" spans="42:73">
+      <c r="AP17" s="30">
+        <f>IF(AR17="","",ROW()-16)</f>
+        <v>1</v>
+      </c>
+      <c r="AQ17" s="31"/>
+      <c r="AR17" s="11" t="s">
+        <v>35</v>
+      </c>
       <c r="AS17" s="12"/>
       <c r="AT17" s="12"/>
-      <c r="AU17" s="13"/>
-      <c r="AV17" s="8"/>
-      <c r="AW17" s="9"/>
-      <c r="AX17" s="9"/>
-      <c r="AY17" s="9"/>
-      <c r="AZ17" s="10"/>
-      <c r="BA17" s="36"/>
-      <c r="BB17" s="37"/>
-      <c r="BC17" s="38"/>
-      <c r="BD17" s="33"/>
-      <c r="BE17" s="34"/>
-      <c r="BF17" s="35"/>
-      <c r="BG17" s="30"/>
-      <c r="BH17" s="32"/>
-      <c r="BI17" s="36"/>
-      <c r="BJ17" s="37"/>
-      <c r="BK17" s="37"/>
-      <c r="BL17" s="38"/>
-      <c r="BM17" s="36"/>
-      <c r="BN17" s="37"/>
-      <c r="BO17" s="37"/>
-      <c r="BP17" s="37"/>
-      <c r="BQ17" s="38"/>
-    </row>
-    <row r="18" spans="42:69">
-      <c r="AP18" s="11"/>
-      <c r="AQ18" s="12"/>
-      <c r="AR18" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="13"/>
+      <c r="AX17" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY17" s="15"/>
+      <c r="AZ17" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="13"/>
+      <c r="BE17" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="13"/>
+      <c r="BH17" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI17" s="12"/>
+      <c r="BJ17" s="13"/>
+      <c r="BK17" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="BL17" s="13"/>
+      <c r="BM17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="BN17" s="9"/>
+      <c r="BO17" s="9"/>
+      <c r="BP17" s="10"/>
+      <c r="BQ17" s="11"/>
+      <c r="BR17" s="12"/>
+      <c r="BS17" s="12"/>
+      <c r="BT17" s="12"/>
+      <c r="BU17" s="13"/>
+    </row>
+    <row r="18" spans="42:73">
+      <c r="AP18" s="30">
+        <f t="shared" ref="AP18:AP28" si="1">IF(AR18="","",ROW()-16)</f>
+        <v>2</v>
+      </c>
+      <c r="AQ18" s="31"/>
+      <c r="AR18" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="AS18" s="12"/>
       <c r="AT18" s="12"/>
-      <c r="AU18" s="13"/>
-      <c r="AV18" s="8"/>
-      <c r="AW18" s="9"/>
-      <c r="AX18" s="9"/>
-      <c r="AY18" s="9"/>
-      <c r="AZ18" s="10"/>
-      <c r="BA18" s="36"/>
-      <c r="BB18" s="37"/>
-      <c r="BC18" s="38"/>
-      <c r="BD18" s="33"/>
-      <c r="BE18" s="34"/>
-      <c r="BF18" s="35"/>
-      <c r="BG18" s="30"/>
-      <c r="BH18" s="32"/>
-      <c r="BI18" s="36"/>
-      <c r="BJ18" s="37"/>
-      <c r="BK18" s="37"/>
-      <c r="BL18" s="38"/>
-      <c r="BM18" s="36"/>
-      <c r="BN18" s="37"/>
-      <c r="BO18" s="37"/>
-      <c r="BP18" s="37"/>
-      <c r="BQ18" s="38"/>
-    </row>
-    <row r="19" spans="42:69">
-      <c r="AP19" s="11"/>
-      <c r="AQ19" s="12"/>
-      <c r="AR19" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="13"/>
+      <c r="AX18" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY18" s="15"/>
+      <c r="AZ18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="13"/>
+      <c r="BE18" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="13"/>
+      <c r="BH18" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="BI18" s="12"/>
+      <c r="BJ18" s="13"/>
+      <c r="BK18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="BL18" s="13"/>
+      <c r="BM18" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="BN18" s="9"/>
+      <c r="BO18" s="9"/>
+      <c r="BP18" s="10"/>
+      <c r="BQ18" s="8"/>
+      <c r="BR18" s="9"/>
+      <c r="BS18" s="9"/>
+      <c r="BT18" s="9"/>
+      <c r="BU18" s="10"/>
+    </row>
+    <row r="19" spans="42:73">
+      <c r="AP19" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ19" s="31"/>
+      <c r="AR19" s="11"/>
       <c r="AS19" s="12"/>
       <c r="AT19" s="12"/>
-      <c r="AU19" s="13"/>
-      <c r="AV19" s="8"/>
-      <c r="AW19" s="9"/>
-      <c r="AX19" s="9"/>
-      <c r="AY19" s="9"/>
-      <c r="AZ19" s="10"/>
-      <c r="BA19" s="36"/>
-      <c r="BB19" s="37"/>
-      <c r="BC19" s="38"/>
-      <c r="BD19" s="30"/>
-      <c r="BE19" s="31"/>
-      <c r="BF19" s="32"/>
-      <c r="BG19" s="30"/>
-      <c r="BH19" s="32"/>
-      <c r="BI19" s="39"/>
-      <c r="BJ19" s="40"/>
-      <c r="BK19" s="40"/>
-      <c r="BL19" s="41"/>
-      <c r="BM19" s="39"/>
-      <c r="BN19" s="40"/>
-      <c r="BO19" s="40"/>
-      <c r="BP19" s="40"/>
-      <c r="BQ19" s="41"/>
-    </row>
-    <row r="20" spans="42:69">
-      <c r="AP20" s="11"/>
-      <c r="AQ20" s="12"/>
-      <c r="AR20" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="13"/>
+      <c r="AX19" s="14"/>
+      <c r="AY19" s="15"/>
+      <c r="AZ19" s="11"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="13"/>
+      <c r="BE19" s="11"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="13"/>
+      <c r="BH19" s="11"/>
+      <c r="BI19" s="12"/>
+      <c r="BJ19" s="13"/>
+      <c r="BK19" s="11"/>
+      <c r="BL19" s="13"/>
+      <c r="BM19" s="8"/>
+      <c r="BN19" s="9"/>
+      <c r="BO19" s="9"/>
+      <c r="BP19" s="10"/>
+      <c r="BQ19" s="11"/>
+      <c r="BR19" s="12"/>
+      <c r="BS19" s="12"/>
+      <c r="BT19" s="12"/>
+      <c r="BU19" s="13"/>
+    </row>
+    <row r="20" spans="42:73">
+      <c r="AP20" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ20" s="31"/>
+      <c r="AR20" s="11"/>
       <c r="AS20" s="12"/>
       <c r="AT20" s="12"/>
-      <c r="AU20" s="13"/>
-      <c r="AV20" s="8"/>
-      <c r="AW20" s="9"/>
-      <c r="AX20" s="9"/>
-      <c r="AY20" s="9"/>
-      <c r="AZ20" s="10"/>
-      <c r="BA20" s="36"/>
-      <c r="BB20" s="37"/>
-      <c r="BC20" s="38"/>
-      <c r="BD20" s="30"/>
-      <c r="BE20" s="31"/>
-      <c r="BF20" s="32"/>
-      <c r="BG20" s="30"/>
-      <c r="BH20" s="32"/>
-      <c r="BI20" s="39"/>
-      <c r="BJ20" s="40"/>
-      <c r="BK20" s="40"/>
-      <c r="BL20" s="41"/>
-      <c r="BM20" s="39"/>
-      <c r="BN20" s="40"/>
-      <c r="BO20" s="40"/>
-      <c r="BP20" s="40"/>
-      <c r="BQ20" s="41"/>
-    </row>
-    <row r="21" spans="42:69">
-      <c r="AP21" s="11"/>
-      <c r="AQ21" s="12"/>
-      <c r="AR21" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="13"/>
+      <c r="AX20" s="14"/>
+      <c r="AY20" s="15"/>
+      <c r="AZ20" s="11"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="13"/>
+      <c r="BE20" s="11"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="13"/>
+      <c r="BH20" s="11"/>
+      <c r="BI20" s="12"/>
+      <c r="BJ20" s="13"/>
+      <c r="BK20" s="11"/>
+      <c r="BL20" s="13"/>
+      <c r="BM20" s="11"/>
+      <c r="BN20" s="12"/>
+      <c r="BO20" s="12"/>
+      <c r="BP20" s="13"/>
+      <c r="BQ20" s="11"/>
+      <c r="BR20" s="12"/>
+      <c r="BS20" s="12"/>
+      <c r="BT20" s="12"/>
+      <c r="BU20" s="13"/>
+    </row>
+    <row r="21" spans="42:73">
+      <c r="AP21" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ21" s="31"/>
+      <c r="AR21" s="11"/>
       <c r="AS21" s="12"/>
       <c r="AT21" s="12"/>
-      <c r="AU21" s="13"/>
-      <c r="AV21" s="8"/>
-      <c r="AW21" s="9"/>
-      <c r="AX21" s="9"/>
-      <c r="AY21" s="9"/>
-      <c r="AZ21" s="10"/>
-      <c r="BA21" s="36"/>
-      <c r="BB21" s="37"/>
-      <c r="BC21" s="38"/>
-      <c r="BD21" s="30"/>
-      <c r="BE21" s="31"/>
-      <c r="BF21" s="32"/>
-      <c r="BG21" s="30"/>
-      <c r="BH21" s="32"/>
-      <c r="BI21" s="39"/>
-      <c r="BJ21" s="40"/>
-      <c r="BK21" s="40"/>
-      <c r="BL21" s="41"/>
-      <c r="BM21" s="39"/>
-      <c r="BN21" s="40"/>
-      <c r="BO21" s="40"/>
-      <c r="BP21" s="40"/>
-      <c r="BQ21" s="41"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="13"/>
+      <c r="AX21" s="14"/>
+      <c r="AY21" s="15"/>
+      <c r="AZ21" s="11"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="13"/>
+      <c r="BE21" s="11"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="13"/>
+      <c r="BH21" s="11"/>
+      <c r="BI21" s="12"/>
+      <c r="BJ21" s="13"/>
+      <c r="BK21" s="11"/>
+      <c r="BL21" s="13"/>
+      <c r="BM21" s="11"/>
+      <c r="BN21" s="12"/>
+      <c r="BO21" s="12"/>
+      <c r="BP21" s="13"/>
+      <c r="BQ21" s="11"/>
+      <c r="BR21" s="12"/>
+      <c r="BS21" s="12"/>
+      <c r="BT21" s="12"/>
+      <c r="BU21" s="13"/>
+    </row>
+    <row r="22" spans="42:73">
+      <c r="AP22" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ22" s="31"/>
+      <c r="AR22" s="11"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="13"/>
+      <c r="AX22" s="14"/>
+      <c r="AY22" s="15"/>
+      <c r="AZ22" s="11"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="13"/>
+      <c r="BE22" s="11"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="13"/>
+      <c r="BH22" s="11"/>
+      <c r="BI22" s="12"/>
+      <c r="BJ22" s="13"/>
+      <c r="BK22" s="11"/>
+      <c r="BL22" s="13"/>
+      <c r="BM22" s="11"/>
+      <c r="BN22" s="12"/>
+      <c r="BO22" s="12"/>
+      <c r="BP22" s="13"/>
+      <c r="BQ22" s="11"/>
+      <c r="BR22" s="12"/>
+      <c r="BS22" s="12"/>
+      <c r="BT22" s="12"/>
+      <c r="BU22" s="13"/>
+    </row>
+    <row r="23" spans="42:73">
+      <c r="AP23" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ23" s="31"/>
+      <c r="AR23" s="11"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="13"/>
+      <c r="AX23" s="14"/>
+      <c r="AY23" s="15"/>
+      <c r="AZ23" s="11"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="13"/>
+      <c r="BE23" s="11"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="13"/>
+      <c r="BH23" s="11"/>
+      <c r="BI23" s="12"/>
+      <c r="BJ23" s="13"/>
+      <c r="BK23" s="11"/>
+      <c r="BL23" s="13"/>
+      <c r="BM23" s="11"/>
+      <c r="BN23" s="12"/>
+      <c r="BO23" s="12"/>
+      <c r="BP23" s="13"/>
+      <c r="BQ23" s="11"/>
+      <c r="BR23" s="12"/>
+      <c r="BS23" s="12"/>
+      <c r="BT23" s="12"/>
+      <c r="BU23" s="13"/>
+    </row>
+    <row r="24" spans="42:73">
+      <c r="AP24" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ24" s="31"/>
+      <c r="AR24" s="11"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="13"/>
+      <c r="AX24" s="14"/>
+      <c r="AY24" s="15"/>
+      <c r="AZ24" s="11"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="13"/>
+      <c r="BE24" s="11"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="13"/>
+      <c r="BH24" s="11"/>
+      <c r="BI24" s="12"/>
+      <c r="BJ24" s="13"/>
+      <c r="BK24" s="11"/>
+      <c r="BL24" s="13"/>
+      <c r="BM24" s="11"/>
+      <c r="BN24" s="12"/>
+      <c r="BO24" s="12"/>
+      <c r="BP24" s="13"/>
+      <c r="BQ24" s="11"/>
+      <c r="BR24" s="12"/>
+      <c r="BS24" s="12"/>
+      <c r="BT24" s="12"/>
+      <c r="BU24" s="13"/>
+    </row>
+    <row r="25" spans="42:73">
+      <c r="AP25" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ25" s="31"/>
+      <c r="AR25" s="11"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="13"/>
+      <c r="AX25" s="14"/>
+      <c r="AY25" s="15"/>
+      <c r="AZ25" s="11"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="13"/>
+      <c r="BE25" s="11"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="13"/>
+      <c r="BH25" s="11"/>
+      <c r="BI25" s="12"/>
+      <c r="BJ25" s="13"/>
+      <c r="BK25" s="11"/>
+      <c r="BL25" s="13"/>
+      <c r="BM25" s="11"/>
+      <c r="BN25" s="12"/>
+      <c r="BO25" s="12"/>
+      <c r="BP25" s="13"/>
+      <c r="BQ25" s="11"/>
+      <c r="BR25" s="12"/>
+      <c r="BS25" s="12"/>
+      <c r="BT25" s="12"/>
+      <c r="BU25" s="13"/>
+    </row>
+    <row r="26" spans="42:73">
+      <c r="AP26" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ26" s="31"/>
+      <c r="AR26" s="11"/>
+      <c r="AS26" s="12"/>
+      <c r="AT26" s="12"/>
+      <c r="AU26" s="12"/>
+      <c r="AV26" s="12"/>
+      <c r="AW26" s="13"/>
+      <c r="AX26" s="14"/>
+      <c r="AY26" s="15"/>
+      <c r="AZ26" s="11"/>
+      <c r="BA26" s="12"/>
+      <c r="BB26" s="12"/>
+      <c r="BC26" s="12"/>
+      <c r="BD26" s="13"/>
+      <c r="BE26" s="11"/>
+      <c r="BF26" s="12"/>
+      <c r="BG26" s="13"/>
+      <c r="BH26" s="11"/>
+      <c r="BI26" s="12"/>
+      <c r="BJ26" s="13"/>
+      <c r="BK26" s="11"/>
+      <c r="BL26" s="13"/>
+      <c r="BM26" s="11"/>
+      <c r="BN26" s="12"/>
+      <c r="BO26" s="12"/>
+      <c r="BP26" s="13"/>
+      <c r="BQ26" s="11"/>
+      <c r="BR26" s="12"/>
+      <c r="BS26" s="12"/>
+      <c r="BT26" s="12"/>
+      <c r="BU26" s="13"/>
+    </row>
+    <row r="27" spans="42:73">
+      <c r="AP27" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ27" s="31"/>
+      <c r="AR27" s="11"/>
+      <c r="AS27" s="12"/>
+      <c r="AT27" s="12"/>
+      <c r="AU27" s="12"/>
+      <c r="AV27" s="12"/>
+      <c r="AW27" s="13"/>
+      <c r="AX27" s="14"/>
+      <c r="AY27" s="15"/>
+      <c r="AZ27" s="11"/>
+      <c r="BA27" s="12"/>
+      <c r="BB27" s="12"/>
+      <c r="BC27" s="12"/>
+      <c r="BD27" s="13"/>
+      <c r="BE27" s="11"/>
+      <c r="BF27" s="12"/>
+      <c r="BG27" s="13"/>
+      <c r="BH27" s="11"/>
+      <c r="BI27" s="12"/>
+      <c r="BJ27" s="13"/>
+      <c r="BK27" s="11"/>
+      <c r="BL27" s="13"/>
+      <c r="BM27" s="11"/>
+      <c r="BN27" s="12"/>
+      <c r="BO27" s="12"/>
+      <c r="BP27" s="13"/>
+      <c r="BQ27" s="11"/>
+      <c r="BR27" s="12"/>
+      <c r="BS27" s="12"/>
+      <c r="BT27" s="12"/>
+      <c r="BU27" s="13"/>
+    </row>
+    <row r="28" spans="42:73">
+      <c r="AP28" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ28" s="31"/>
+      <c r="AR28" s="11"/>
+      <c r="AS28" s="12"/>
+      <c r="AT28" s="12"/>
+      <c r="AU28" s="12"/>
+      <c r="AV28" s="12"/>
+      <c r="AW28" s="13"/>
+      <c r="AX28" s="14"/>
+      <c r="AY28" s="15"/>
+      <c r="AZ28" s="11"/>
+      <c r="BA28" s="12"/>
+      <c r="BB28" s="12"/>
+      <c r="BC28" s="12"/>
+      <c r="BD28" s="13"/>
+      <c r="BE28" s="11"/>
+      <c r="BF28" s="12"/>
+      <c r="BG28" s="13"/>
+      <c r="BH28" s="11"/>
+      <c r="BI28" s="12"/>
+      <c r="BJ28" s="13"/>
+      <c r="BK28" s="11"/>
+      <c r="BL28" s="13"/>
+      <c r="BM28" s="11"/>
+      <c r="BN28" s="12"/>
+      <c r="BO28" s="12"/>
+      <c r="BP28" s="13"/>
+      <c r="BQ28" s="11"/>
+      <c r="BR28" s="12"/>
+      <c r="BS28" s="12"/>
+      <c r="BT28" s="12"/>
+      <c r="BU28" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="101">
-    <mergeCell ref="BI21:BL21"/>
-    <mergeCell ref="BM21:BQ21"/>
-    <mergeCell ref="BI13:BL13"/>
-    <mergeCell ref="BM13:BQ13"/>
-    <mergeCell ref="BI14:BL14"/>
-    <mergeCell ref="BM14:BQ14"/>
-    <mergeCell ref="BI15:BL15"/>
-    <mergeCell ref="BM15:BQ15"/>
-    <mergeCell ref="BI18:BL18"/>
-    <mergeCell ref="BM18:BQ18"/>
-    <mergeCell ref="BI19:BL19"/>
-    <mergeCell ref="BM19:BQ19"/>
-    <mergeCell ref="BI20:BL20"/>
-    <mergeCell ref="BM20:BQ20"/>
-    <mergeCell ref="BA21:BC21"/>
-    <mergeCell ref="BD18:BF18"/>
-    <mergeCell ref="BD19:BF19"/>
-    <mergeCell ref="BD20:BF20"/>
-    <mergeCell ref="BD21:BF21"/>
-    <mergeCell ref="BD16:BF16"/>
-    <mergeCell ref="BG21:BH21"/>
-    <mergeCell ref="BG16:BH16"/>
-    <mergeCell ref="BG17:BH17"/>
-    <mergeCell ref="BG18:BH18"/>
-    <mergeCell ref="BG19:BH19"/>
-    <mergeCell ref="BG20:BH20"/>
-    <mergeCell ref="AP4:AU4"/>
-    <mergeCell ref="BA15:BC15"/>
-    <mergeCell ref="BA16:BC16"/>
-    <mergeCell ref="BA17:BC17"/>
-    <mergeCell ref="BA18:BC18"/>
-    <mergeCell ref="BA19:BC19"/>
-    <mergeCell ref="BA20:BC20"/>
-    <mergeCell ref="BA9:BC9"/>
-    <mergeCell ref="BA10:BC10"/>
-    <mergeCell ref="BA11:BC11"/>
-    <mergeCell ref="BA12:BC12"/>
-    <mergeCell ref="BA13:BC13"/>
-    <mergeCell ref="BA14:BC14"/>
-    <mergeCell ref="AP20:AU20"/>
-    <mergeCell ref="AV4:BQ4"/>
-    <mergeCell ref="AV5:BQ5"/>
-    <mergeCell ref="BI7:BL8"/>
-    <mergeCell ref="BM7:BQ8"/>
-    <mergeCell ref="BI9:BL9"/>
-    <mergeCell ref="BM9:BQ9"/>
-    <mergeCell ref="BG9:BH9"/>
-    <mergeCell ref="BI16:BL16"/>
-    <mergeCell ref="BM16:BQ16"/>
-    <mergeCell ref="BI17:BL17"/>
-    <mergeCell ref="BM17:BQ17"/>
-    <mergeCell ref="BI10:BL10"/>
-    <mergeCell ref="BM10:BQ10"/>
-    <mergeCell ref="BD13:BF13"/>
-    <mergeCell ref="BD14:BF14"/>
-    <mergeCell ref="BD15:BF15"/>
-    <mergeCell ref="BG10:BH10"/>
-    <mergeCell ref="BG11:BH11"/>
-    <mergeCell ref="BG12:BH12"/>
-    <mergeCell ref="BG13:BH13"/>
-    <mergeCell ref="BG14:BH14"/>
-    <mergeCell ref="BG15:BH15"/>
-    <mergeCell ref="BI11:BL11"/>
-    <mergeCell ref="BM11:BQ11"/>
-    <mergeCell ref="BI12:BL12"/>
-    <mergeCell ref="BM12:BQ12"/>
-    <mergeCell ref="BA7:BC8"/>
-    <mergeCell ref="BD7:BF8"/>
-    <mergeCell ref="AP18:AU18"/>
-    <mergeCell ref="AP19:AU19"/>
-    <mergeCell ref="BG7:BH8"/>
-    <mergeCell ref="AP9:AU9"/>
-    <mergeCell ref="AP10:AU10"/>
-    <mergeCell ref="AP11:AU11"/>
-    <mergeCell ref="AP12:AU12"/>
-    <mergeCell ref="BD9:BF9"/>
-    <mergeCell ref="BD10:BF10"/>
-    <mergeCell ref="BD11:BF11"/>
-    <mergeCell ref="BD12:BF12"/>
-    <mergeCell ref="AV10:AZ10"/>
-    <mergeCell ref="AV11:AZ11"/>
-    <mergeCell ref="AV12:AZ12"/>
-    <mergeCell ref="AV13:AZ13"/>
-    <mergeCell ref="AV14:AZ14"/>
-    <mergeCell ref="AP13:AU13"/>
-    <mergeCell ref="AP14:AU14"/>
-    <mergeCell ref="AP15:AU15"/>
-    <mergeCell ref="AP16:AU16"/>
-    <mergeCell ref="AP17:AU17"/>
-    <mergeCell ref="BD17:BF17"/>
-    <mergeCell ref="AV20:AZ20"/>
-    <mergeCell ref="AV21:AZ21"/>
-    <mergeCell ref="AV15:AZ15"/>
-    <mergeCell ref="AV16:AZ16"/>
-    <mergeCell ref="AV17:AZ17"/>
-    <mergeCell ref="AV18:AZ18"/>
-    <mergeCell ref="AV19:AZ19"/>
-    <mergeCell ref="AP5:AU5"/>
-    <mergeCell ref="AP7:AU8"/>
-    <mergeCell ref="AV7:AZ8"/>
-    <mergeCell ref="AP21:AU21"/>
+  <mergeCells count="179">
+    <mergeCell ref="AP28:AQ28"/>
+    <mergeCell ref="AR28:AW28"/>
+    <mergeCell ref="AX28:AY28"/>
+    <mergeCell ref="AZ28:BD28"/>
+    <mergeCell ref="BE28:BG28"/>
+    <mergeCell ref="BH28:BJ28"/>
+    <mergeCell ref="BK28:BL28"/>
+    <mergeCell ref="BM28:BP28"/>
+    <mergeCell ref="BQ28:BU28"/>
+    <mergeCell ref="AP27:AQ27"/>
+    <mergeCell ref="AR27:AW27"/>
+    <mergeCell ref="AX27:AY27"/>
+    <mergeCell ref="AZ27:BD27"/>
+    <mergeCell ref="BE27:BG27"/>
+    <mergeCell ref="BH27:BJ27"/>
+    <mergeCell ref="BK27:BL27"/>
+    <mergeCell ref="BM27:BP27"/>
+    <mergeCell ref="BQ27:BU27"/>
+    <mergeCell ref="AP26:AQ26"/>
+    <mergeCell ref="AR26:AW26"/>
+    <mergeCell ref="AX26:AY26"/>
+    <mergeCell ref="AZ26:BD26"/>
+    <mergeCell ref="BE26:BG26"/>
+    <mergeCell ref="BH26:BJ26"/>
+    <mergeCell ref="BK26:BL26"/>
+    <mergeCell ref="BM26:BP26"/>
+    <mergeCell ref="BQ26:BU26"/>
+    <mergeCell ref="AP25:AQ25"/>
+    <mergeCell ref="AR25:AW25"/>
+    <mergeCell ref="AX25:AY25"/>
+    <mergeCell ref="AZ25:BD25"/>
+    <mergeCell ref="BE25:BG25"/>
+    <mergeCell ref="BH25:BJ25"/>
+    <mergeCell ref="BK25:BL25"/>
+    <mergeCell ref="BM25:BP25"/>
+    <mergeCell ref="BQ25:BU25"/>
+    <mergeCell ref="AP24:AQ24"/>
+    <mergeCell ref="AR24:AW24"/>
+    <mergeCell ref="AX24:AY24"/>
+    <mergeCell ref="AZ24:BD24"/>
+    <mergeCell ref="BE24:BG24"/>
+    <mergeCell ref="BH24:BJ24"/>
+    <mergeCell ref="BK24:BL24"/>
+    <mergeCell ref="BM24:BP24"/>
+    <mergeCell ref="BQ24:BU24"/>
+    <mergeCell ref="AP23:AQ23"/>
+    <mergeCell ref="AR23:AW23"/>
+    <mergeCell ref="AX23:AY23"/>
+    <mergeCell ref="AZ23:BD23"/>
+    <mergeCell ref="BE23:BG23"/>
+    <mergeCell ref="BH23:BJ23"/>
+    <mergeCell ref="BK23:BL23"/>
+    <mergeCell ref="BM23:BP23"/>
+    <mergeCell ref="BQ23:BU23"/>
+    <mergeCell ref="AP22:AQ22"/>
+    <mergeCell ref="AR22:AW22"/>
+    <mergeCell ref="AX22:AY22"/>
+    <mergeCell ref="AZ22:BD22"/>
+    <mergeCell ref="BE22:BG22"/>
+    <mergeCell ref="BH22:BJ22"/>
+    <mergeCell ref="BK22:BL22"/>
+    <mergeCell ref="BM22:BP22"/>
+    <mergeCell ref="BQ22:BU22"/>
+    <mergeCell ref="AP21:AQ21"/>
+    <mergeCell ref="AR21:AW21"/>
+    <mergeCell ref="AX21:AY21"/>
+    <mergeCell ref="AZ21:BD21"/>
+    <mergeCell ref="BE21:BG21"/>
+    <mergeCell ref="BH21:BJ21"/>
+    <mergeCell ref="BK21:BL21"/>
+    <mergeCell ref="BM21:BP21"/>
+    <mergeCell ref="BQ21:BU21"/>
+    <mergeCell ref="AP20:AQ20"/>
+    <mergeCell ref="AR20:AW20"/>
+    <mergeCell ref="AX20:AY20"/>
+    <mergeCell ref="AZ20:BD20"/>
+    <mergeCell ref="BE20:BG20"/>
+    <mergeCell ref="BH20:BJ20"/>
+    <mergeCell ref="BK20:BL20"/>
+    <mergeCell ref="BM20:BP20"/>
+    <mergeCell ref="BQ20:BU20"/>
+    <mergeCell ref="AP19:AQ19"/>
+    <mergeCell ref="AR19:AW19"/>
+    <mergeCell ref="AX19:AY19"/>
+    <mergeCell ref="AZ19:BD19"/>
+    <mergeCell ref="BE19:BG19"/>
+    <mergeCell ref="BH19:BJ19"/>
+    <mergeCell ref="BK19:BL19"/>
+    <mergeCell ref="BM19:BP19"/>
+    <mergeCell ref="BQ19:BU19"/>
+    <mergeCell ref="AP18:AQ18"/>
+    <mergeCell ref="AR18:AW18"/>
+    <mergeCell ref="AX18:AY18"/>
+    <mergeCell ref="AZ18:BD18"/>
+    <mergeCell ref="BE18:BG18"/>
+    <mergeCell ref="BH18:BJ18"/>
+    <mergeCell ref="BK18:BL18"/>
+    <mergeCell ref="BM18:BP18"/>
+    <mergeCell ref="BQ18:BU18"/>
+    <mergeCell ref="AP17:AQ17"/>
+    <mergeCell ref="AR17:AW17"/>
+    <mergeCell ref="AX17:AY17"/>
+    <mergeCell ref="AZ17:BD17"/>
+    <mergeCell ref="BE17:BG17"/>
+    <mergeCell ref="BH17:BJ17"/>
+    <mergeCell ref="BK17:BL17"/>
+    <mergeCell ref="BM17:BP17"/>
+    <mergeCell ref="BQ17:BU17"/>
+    <mergeCell ref="AU14:BB14"/>
+    <mergeCell ref="BC14:BH14"/>
+    <mergeCell ref="BI14:BU14"/>
+    <mergeCell ref="AP15:AQ16"/>
+    <mergeCell ref="AR15:AW16"/>
+    <mergeCell ref="AX15:AY16"/>
+    <mergeCell ref="AZ15:BD16"/>
+    <mergeCell ref="BE15:BG16"/>
+    <mergeCell ref="BH15:BJ16"/>
+    <mergeCell ref="BK15:BL16"/>
+    <mergeCell ref="BM15:BP16"/>
+    <mergeCell ref="BQ15:BU16"/>
+    <mergeCell ref="BE9:BG9"/>
+    <mergeCell ref="BH9:BJ9"/>
+    <mergeCell ref="BK9:BL9"/>
+    <mergeCell ref="BM9:BP9"/>
+    <mergeCell ref="BQ9:BU9"/>
+    <mergeCell ref="AP10:AQ10"/>
+    <mergeCell ref="AR10:AW10"/>
+    <mergeCell ref="AX10:AY10"/>
+    <mergeCell ref="AZ10:BD10"/>
+    <mergeCell ref="BE10:BG10"/>
+    <mergeCell ref="BH10:BJ10"/>
+    <mergeCell ref="BK10:BL10"/>
+    <mergeCell ref="BM10:BP10"/>
+    <mergeCell ref="BQ10:BU10"/>
+    <mergeCell ref="BE7:BG7"/>
+    <mergeCell ref="BH7:BJ7"/>
+    <mergeCell ref="BK7:BL7"/>
+    <mergeCell ref="BM7:BP7"/>
+    <mergeCell ref="BQ7:BU7"/>
+    <mergeCell ref="AP8:AQ8"/>
+    <mergeCell ref="AR8:AW8"/>
+    <mergeCell ref="AX8:AY8"/>
+    <mergeCell ref="AZ8:BD8"/>
+    <mergeCell ref="BE8:BG8"/>
+    <mergeCell ref="BH8:BJ8"/>
+    <mergeCell ref="BK8:BL8"/>
+    <mergeCell ref="BM8:BP8"/>
+    <mergeCell ref="BQ8:BU8"/>
+    <mergeCell ref="AP4:AT4"/>
+    <mergeCell ref="AU4:BB4"/>
+    <mergeCell ref="BC4:BH4"/>
+    <mergeCell ref="BI4:BU4"/>
+    <mergeCell ref="AP5:AQ6"/>
+    <mergeCell ref="AR5:AW6"/>
+    <mergeCell ref="AX5:AY6"/>
+    <mergeCell ref="AZ5:BD6"/>
+    <mergeCell ref="BE5:BG6"/>
+    <mergeCell ref="BH5:BJ6"/>
+    <mergeCell ref="BK5:BL6"/>
+    <mergeCell ref="BM5:BP6"/>
+    <mergeCell ref="BQ5:BU6"/>
+    <mergeCell ref="AP7:AQ7"/>
+    <mergeCell ref="AR7:AW7"/>
+    <mergeCell ref="AX7:AY7"/>
+    <mergeCell ref="AZ7:BD7"/>
+    <mergeCell ref="AP9:AQ9"/>
+    <mergeCell ref="AR9:AW9"/>
+    <mergeCell ref="AX9:AY9"/>
+    <mergeCell ref="AZ9:BD9"/>
+    <mergeCell ref="AP11:AQ11"/>
+    <mergeCell ref="AR11:AW11"/>
+    <mergeCell ref="AX11:AY11"/>
+    <mergeCell ref="AZ11:BD11"/>
+    <mergeCell ref="AP14:AT14"/>
+    <mergeCell ref="BE11:BG11"/>
+    <mergeCell ref="BH11:BJ11"/>
+    <mergeCell ref="BK11:BL11"/>
+    <mergeCell ref="BM11:BP11"/>
+    <mergeCell ref="BQ11:BU11"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="AP7:BU11">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+      <formula>$AR7=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP17:BU28">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$AR17=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AZ7:BD11 AZ17:BD28" xr:uid="{42E6519B-C5B9-454D-BB81-27E76D563881}">
+      <formula1>"-,Zen Kaku Gothic New"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX17:AY28 AX7:AY11" xr:uid="{2E8FED39-B8F5-E649-AE2E-DE6304939CDA}">
+      <formula1>"○,-"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
